--- a/data/dividends_info_20260803.xlsx
+++ b/data/dividends_info_20260803.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>45.25500106811523</v>
+        <v>45.27000045776367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1988730480075278</v>
+        <v>0.1988071550473449</v>
       </c>
       <c r="J2" t="n">
         <v>224</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66.09999847412109</v>
+        <v>66.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.05900153730572</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="J3" t="n">
         <v>203</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4740000069141388</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.8438818442305566</v>
       </c>
       <c r="J5" t="n">
         <v>133</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45.25500106811523</v>
+        <v>45.27000045776367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1988730480075278</v>
+        <v>0.1988071550473449</v>
       </c>
       <c r="J6" t="n">
         <v>133</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.134999990463257</v>
+        <v>2.130000114440918</v>
       </c>
       <c r="I7" t="n">
-        <v>3.606557393159162</v>
+        <v>3.615023279949961</v>
       </c>
       <c r="J7" t="n">
         <v>112</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.57500076293945</v>
+        <v>23.69499969482422</v>
       </c>
       <c r="I8" t="n">
-        <v>1.145280980963731</v>
+        <v>1.139480917819877</v>
       </c>
       <c r="J8" t="n">
         <v>112</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.900000095367432</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I9" t="n">
-        <v>3.389830453681454</v>
+        <v>3.378378334839559</v>
       </c>
       <c r="J9" t="n">
         <v>105</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4740000069141388</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.8438818442305566</v>
       </c>
       <c r="J11" t="n">
         <v>77</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.059999942779541</v>
+        <v>5.019999980926514</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7509881507849578</v>
+        <v>0.7569721144298999</v>
       </c>
       <c r="J13" t="n">
         <v>56</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.56999969482422</v>
+        <v>23.69499969482422</v>
       </c>
       <c r="I14" t="n">
-        <v>1.145523985981594</v>
+        <v>1.139480917819877</v>
       </c>
       <c r="J14" t="n">
         <v>49</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.975000023841858</v>
+        <v>1.97599995136261</v>
       </c>
       <c r="I15" t="n">
-        <v>2.88607591452688</v>
+        <v>2.884615455617494</v>
       </c>
       <c r="J15" t="n">
         <v>49</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>45.25500106811523</v>
+        <v>45.27000045776367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1988730480075278</v>
+        <v>0.1988071550473449</v>
       </c>
       <c r="J16" t="n">
         <v>49</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>93.05000305175781</v>
+        <v>95.69999694824219</v>
       </c>
       <c r="I17" t="n">
-        <v>1.429339018140822</v>
+        <v>1.389759709939499</v>
       </c>
       <c r="J17" t="n">
         <v>49</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.739999771118164</v>
+        <v>5.78000020980835</v>
       </c>
       <c r="I18" t="n">
-        <v>5.226481044642261</v>
+        <v>5.190311230281897</v>
       </c>
       <c r="J18" t="n">
         <v>42</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4740000069141388</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.8438818442305566</v>
       </c>
       <c r="J19" t="n">
         <v>21</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.019999980926514</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>7.284768257929115</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="J20" t="n">
         <v>7</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.059999942779541</v>
+        <v>5.019999980926514</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7509881507849578</v>
+        <v>0.7569721144298999</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.869999885559082</v>
+        <v>2.890000104904175</v>
       </c>
       <c r="I23" t="n">
-        <v>5.155714491297804</v>
+        <v>5.12003441622388</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.650000095367432</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I24" t="n">
-        <v>4.424778686375261</v>
+        <v>4.385965059044991</v>
       </c>
       <c r="J24" t="n">
         <v>-7</v>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.079999923706055</v>
+        <v>4.039999961853027</v>
       </c>
       <c r="I25" t="n">
-        <v>3.431372613184548</v>
+        <v>3.465346567374377</v>
       </c>
       <c r="J25" t="n">
         <v>-14</v>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9.852999687194824</v>
+        <v>9.911999702453613</v>
       </c>
       <c r="I26" t="n">
-        <v>2.638790299952021</v>
+        <v>2.623083210299529</v>
       </c>
       <c r="J26" t="n">
         <v>-14</v>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>13.61999988555908</v>
+        <v>13.73999977111816</v>
       </c>
       <c r="I27" t="n">
-        <v>4.405286380627387</v>
+        <v>4.366812299816886</v>
       </c>
       <c r="J27" t="n">
         <v>-14</v>
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.650000095367432</v>
+        <v>2.657999992370605</v>
       </c>
       <c r="I28" t="n">
-        <v>8.301886493686947</v>
+        <v>8.276899948513067</v>
       </c>
       <c r="J28" t="n">
         <v>-14</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4740000069141388</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.8438818442305566</v>
       </c>
       <c r="J29" t="n">
         <v>-14</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6.659999847412109</v>
+        <v>6.670000076293945</v>
       </c>
       <c r="I30" t="n">
-        <v>3.603603686166109</v>
+        <v>3.598200858392663</v>
       </c>
       <c r="J30" t="n">
         <v>-14</v>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>8.449999809265137</v>
+        <v>8.649999618530273</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5917159896876767</v>
+        <v>0.5780347075725714</v>
       </c>
       <c r="J34" t="n">
         <v>-21</v>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>2.940000057220459</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>5.102040717026832</v>
       </c>
       <c r="J35" t="n">
         <v>-21</v>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.079999923706055</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I36" t="n">
-        <v>4.086538611431805</v>
+        <v>4.047619231433834</v>
       </c>
       <c r="J36" t="n">
         <v>-28</v>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4.489999771118164</v>
+        <v>4.480000019073486</v>
       </c>
       <c r="I37" t="n">
-        <v>1.559020124015899</v>
+        <v>1.562499993347696</v>
       </c>
       <c r="J37" t="n">
         <v>-28</v>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>37.65000152587891</v>
+        <v>37.90000152587891</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3984063583553822</v>
+        <v>0.3957783481817986</v>
       </c>
       <c r="J38" t="n">
         <v>-28</v>
@@ -3634,61 +3634,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BUZZI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Itway S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>